--- a/output/full_scan/batch_seq8_2026-10-19.xlsx
+++ b/output/full_scan/batch_seq8_2026-10-19.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>886.0092905984249</v>
+        <v>1196.009290598426</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>125</v>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>62.4917983090208</v>
+        <v>62.49179848846985</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>12.23537844497552</v>
+        <v>12.2353784412186</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>6.635341076466762</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.4481559507291014</v>
+        <v>0.4481559489265171</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, williams_r_recovery, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, williams_r_recovery, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8021</v>
+        <v>6925</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>799.3677057974215</v>
+        <v>881.7972130438548</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>520</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,13 +605,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>55.97259087257434</v>
+        <v>78.91047455589049</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>21.40878380506365</v>
+        <v>49.02547825660179</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.972585665654046</v>
+        <v>4.279721304385478</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-4.884682070787743</v>
+        <v>1.891655226213565</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6925</v>
+        <v>6869</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>681.7972130438548</v>
+        <v>879.8653768867316</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>93.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>78.91047446162314</v>
+        <v>62.57181542991548</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>49.02547827551045</v>
+        <v>17.433410781634</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4.279721304385478</v>
+        <v>1.354281125833838</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.891655226814432</v>
+        <v>0.1626368516360552</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6934</v>
+        <v>6957</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>642.8810292752785</v>
+        <v>878.4403586626019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>88.5</v>
+        <v>501</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>71.89290504438415</v>
+        <v>87.71724861122786</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>24.30030816735717</v>
+        <v>65.53105174243647</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.388102927527852</v>
+        <v>1.376693738733113</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.389107576791905</v>
+        <v>7.050543457009553</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7810</v>
+        <v>6885</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>641.6717822785232</v>
+        <v>855.9887676467578</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>226.5</v>
+        <v>31.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>46.86692140543651</v>
+        <v>58.405086691498</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>28.82396504471946</v>
+        <v>46.22953973016693</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.4971147385808632</v>
+        <v>0.8224852691954931</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-2.232357892970422</v>
+        <v>-0.0275666600048571</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7712</v>
+        <v>6934</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>631.2159547718953</v>
+        <v>842.8810292752785</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>147.5</v>
+        <v>88.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>36.95288170900572</v>
+        <v>71.89290502999077</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>25.41921947790966</v>
+        <v>24.30030816913692</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.6750356836633701</v>
+        <v>2.388102927527852</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,11 +835,11 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-2.644535965469472</v>
+        <v>1.389107576984175</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>627.6755144081941</v>
+        <v>797.675514408194</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>194.5</v>
@@ -873,7 +873,7 @@
         <v>55.08254817058437</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>37.64013078197917</v>
+        <v>37.64013082238993</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>0.5976916602627438</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.6433663553263083</v>
+        <v>0.6433663554464735</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7711</v>
+        <v>8021</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>613.3085757690901</v>
+        <v>784.3677057974215</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>568</v>
+        <v>520</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>49.84697039018711</v>
+        <v>55.97259093006348</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>28.09362986321453</v>
+        <v>21.40878396770944</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.5245121402047087</v>
+        <v>2.972585665654046</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-7.774851074975512</v>
+        <v>-4.884682072686495</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7751</v>
+        <v>6933</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>612.5595222195898</v>
+        <v>775.7690727262418</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1500</v>
+        <v>406.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>45.26263654420377</v>
+        <v>60.1501834079442</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>12.92432198022774</v>
+        <v>50.07066884782984</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.8904827082225264</v>
+        <v>2.298259715884424</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-7.303509854545862</v>
+        <v>0.2262772290830526</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6869</v>
+        <v>6877</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>599.8653768867316</v>
+        <v>765.6274909643975</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>72.5</v>
+        <v>152.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>62.57181511221333</v>
+        <v>61.18627431856078</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>17.43341085302065</v>
+        <v>27.29468543219988</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.354281125833838</v>
+        <v>3.162749096439749</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.1626368525974422</v>
+        <v>2.15759782700504</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6933</v>
+        <v>7810</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>590.7690727262418</v>
+        <v>756.6717822785232</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>406.5</v>
+        <v>226.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>60.15018335016155</v>
+        <v>46.86692162614593</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>50.0706688762854</v>
+        <v>28.82396518322465</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.298259715884424</v>
+        <v>0.4971147385808632</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.2262772294435748</v>
+        <v>-2.232357895614202</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6885</v>
+        <v>6952</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>580.9887676467579</v>
+        <v>722.1610129174903</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>31.5</v>
+        <v>39.6</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>58.40508653195869</v>
+        <v>52.85200116614844</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46.22953957877351</v>
+        <v>6.925878049181798</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.8224852691954931</v>
+        <v>0.1448009161442579</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.0275666596443409</v>
+        <v>0.2305873496338142</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6957</v>
+        <v>6838</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>568.4403586626019</v>
+        <v>706.9140435689512</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>501</v>
+        <v>25.3</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>87.71724860834507</v>
+        <v>58.25040096417182</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>65.53105189583765</v>
+        <v>30.73560745313613</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.376693738733113</v>
+        <v>0.5442382392098709</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>7.050543456889344</v>
+        <v>-0.0440831858989377</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8028</v>
+        <v>6997</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>565.7745014747613</v>
+        <v>701.4382031952159</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>260</v>
+        <v>68.8</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>46.67065680854395</v>
+        <v>53.3093428848672</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>23.90046166655383</v>
+        <v>9.55100389796425</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.4768351338741992</v>
+        <v>1.648498357306214</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-2.8400735017369</v>
+        <v>0.6616921114064307</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6877</v>
+        <v>6894</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>565.6274909643976</v>
+        <v>681.2842744741641</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>152.5</v>
+        <v>370.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>61.18627433024251</v>
+        <v>52.3732650893713</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>27.29468546471137</v>
+        <v>33.91067845905138</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3.162749096439749</v>
+        <v>0.8177923151517713</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>1</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>2.15759782625998</v>
+        <v>0.7917298805118849</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6944</v>
+        <v>8016</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>544.0176257980828</v>
+        <v>675.6404421286937</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>768</v>
+        <v>296.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>47.57359805239862</v>
+        <v>55.80574844918131</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>28.62243751917868</v>
+        <v>17.50357262678953</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.561717922243679</v>
+        <v>1.161093207483207</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-3.969894179403053</v>
+        <v>1.517081469141879</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6894</v>
+        <v>6870</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>541.2842744741641</v>
+        <v>664.6307006442386</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>370.5</v>
+        <v>314</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>52.37326509645276</v>
+        <v>53.97619271288503</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>33.910678444389</v>
+        <v>26.21716891193842</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.8177923151517713</v>
+        <v>1.412292607887117</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.791729880271526</v>
+        <v>-3.068345376430249</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6924</v>
+        <v>7556</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>541.0805947857351</v>
+        <v>661.8144797282581</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>141</v>
+        <v>280</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>54.41687550054905</v>
+        <v>56.70414514539267</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>34.79907092541497</v>
+        <v>32.46359754841635</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.5570166587201594</v>
+        <v>0.5966344247277748</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.1960601511493083</v>
+        <v>-0.5075770097384886</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6997</v>
+        <v>6861</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>531.4382031952163</v>
+        <v>657.3732484527116</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>68.8</v>
+        <v>241.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>53.30934289117238</v>
+        <v>46.25850622647392</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>9.551003897964252</v>
+        <v>30.61946363553416</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.648498357306214</v>
+        <v>0.2708625856534628</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.6616921114064307</v>
+        <v>-6.285568711980076</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6870</v>
+        <v>6924</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>524.6307006442386</v>
+        <v>656.0805947857351</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>314</v>
+        <v>141</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>53.97619269341481</v>
+        <v>54.41687551517473</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>26.21716888378043</v>
+        <v>34.79907089656062</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.412292607887117</v>
+        <v>0.5570166587201594</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-3.068345376069781</v>
+        <v>0.1960601510291573</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7556</v>
+        <v>7712</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>521.8144797282581</v>
+        <v>631.2159547718953</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>280</v>
+        <v>147.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>56.70414510889149</v>
+        <v>36.95288172997179</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>32.46359756543345</v>
+        <v>25.41921948052783</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5966344247277748</v>
+        <v>0.6750356836633701</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.5075770100990269</v>
+        <v>-2.644535962344972</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8016</v>
+        <v>7711</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>505.6404421286937</v>
+        <v>613.3085757690901</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>296.5</v>
+        <v>568</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>55.80574842604396</v>
+        <v>49.84697037614166</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>17.50357262678953</v>
+        <v>28.09362995498709</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.161093207483207</v>
+        <v>0.5245121402047087</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.517081469021757</v>
+        <v>-7.774851074735189</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6903</v>
+        <v>7751</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>488.3055777133699</v>
+        <v>612.5595222195898</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>317</v>
+        <v>1500</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,49 +1718,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>48.45925337541286</v>
+        <v>45.26263650454877</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>25.43670301814178</v>
+        <v>12.924321961461</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.8925785151309583</v>
+        <v>0.8904827082225264</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.8509541392692777</v>
+        <v>-7.303509850460184</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>7792</v>
+        <v>6916</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>478.2518655261243</v>
+        <v>612.0678257114315</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>349.5</v>
+        <v>19.2</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>43.29934577091695</v>
+        <v>56.31800855295705</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>40.8755295724075</v>
+        <v>27.98323495980911</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.3716043502150292</v>
+        <v>0.6194968707256754</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>1</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-11.76257687707755</v>
+        <v>0.0579159190261197</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6916</v>
+        <v>7738</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>472.0678257114316</v>
+        <v>610.4318906041101</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>19.2</v>
+        <v>163</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>56.31800850085931</v>
+        <v>53.37986946286407</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>27.98323496770537</v>
+        <v>19.04892691665153</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.6194968707256754</v>
+        <v>1.343189060411005</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.0579159190141019</v>
+        <v>1.157369523833277</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>7717</v>
+        <v>6903</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>469.4005400020205</v>
+        <v>603.30557771337</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>467</v>
+        <v>317</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>39.5999425895422</v>
+        <v>48.45925343187316</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>17.27250480982931</v>
+        <v>25.43670292007268</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.219660321070874</v>
+        <v>0.8925785151309583</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-17.9594855312418</v>
+        <v>0.850954140471015</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7795</v>
+        <v>6988</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>464.3212730868725</v>
+        <v>592.3215774628485</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>444.5</v>
+        <v>12.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>35.5390246703877</v>
+        <v>54.53236936115071</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>20.17749126305861</v>
+        <v>21.68543190414756</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.9706434388802212</v>
+        <v>0.3143055459979225</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-8.74603957975569</v>
+        <v>0.0604579172664649</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6861</v>
+        <v>7736</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>452.3732484527117</v>
+        <v>589.6942432341144</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>241.5</v>
+        <v>68.3</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>46.25850626400145</v>
+        <v>43.37990984729529</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>30.61946366443314</v>
+        <v>25.94258627515034</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.2708625856534628</v>
+        <v>0.1522843709810039</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-6.285568713229919</v>
+        <v>-0.1491805293571448</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6988</v>
+        <v>6936</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>452.3215774628485</v>
+        <v>587.5419806790435</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>12.5</v>
+        <v>32.4</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>54.53236959862261</v>
+        <v>56.17101725577516</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>21.68543186194866</v>
+        <v>14.80898149266483</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.3143055459979225</v>
+        <v>0.9657392346545672</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0604579172544466</v>
+        <v>0.0483272839533555</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6913</v>
+        <v>7714</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>444.2712200497298</v>
+        <v>576.6621405507393</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>132.5</v>
+        <v>164.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>47.67538835416271</v>
+        <v>46.2574989051737</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>19.36901206525929</v>
+        <v>22.19682264741817</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.6588502806153753</v>
+        <v>0.3531606902755571</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.7826850922485163</v>
+        <v>-0.6063139027265195</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6952</v>
+        <v>8028</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>442.1610129174905</v>
+        <v>565.7745014747613</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>39.6</v>
+        <v>260</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>52.85200115660074</v>
+        <v>46.67065673198578</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>6.925878035610211</v>
+        <v>23.90046158077028</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.1448009161442579</v>
+        <v>0.4768351338741992</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.2305873496458366</v>
+        <v>-2.84007349969398</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7738</v>
+        <v>6928</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>440.4318906041101</v>
+        <v>557.8192056059987</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>163</v>
+        <v>45.2</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>53.37986940698021</v>
+        <v>45.33988192307662</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>19.04892688105886</v>
+        <v>14.16178159067298</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.343189060411005</v>
+        <v>0.7277594894593087</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>1.157369523592932</v>
+        <v>0.1195796331016381</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7714</v>
+        <v>6971</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>436.6621405507393</v>
+        <v>554.9297131650719</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>164.5</v>
+        <v>24.7</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>46.25749891387445</v>
+        <v>53.17782011766752</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>22.19682257198283</v>
+        <v>20.69518752721504</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.3531606902755571</v>
+        <v>0.8566659194435436</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.6063139041685962</v>
+        <v>0.1893341193453908</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6996</v>
+        <v>7839</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>428.2943866253118</v>
+        <v>554.7679540778267</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>160.5</v>
+        <v>43.75</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>32.9194790731875</v>
+        <v>48.25998018308816</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>21.53791141289782</v>
+        <v>21.26416941750654</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>3.963199006012581</v>
+        <v>1.005531904045683</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.2185877678152001</v>
+        <v>0.09733566131654189</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6838</v>
+        <v>6909</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>426.9140435689512</v>
+        <v>549.1424592687365</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>25.3</v>
+        <v>47.4</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>58.25040059546875</v>
+        <v>60.90540335030273</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>30.7356073502536</v>
+        <v>36.10643528216789</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5442382392098709</v>
+        <v>1.27718768239296</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.0440831857306961</v>
+        <v>0.4448768249570138</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>7769</v>
+        <v>6944</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>423.9763644016297</v>
+        <v>544.0176257980828</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>5400</v>
+        <v>768</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>41.31489805863646</v>
+        <v>47.57359796939722</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>14.0260109956222</v>
+        <v>28.62243752889414</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6389495184223923</v>
+        <v>0.561717922243679</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-44.52705702834547</v>
+        <v>-3.96989417459616</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6936</v>
+        <v>6996</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>417.5419806790434</v>
+        <v>543.2943866253119</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>32.4</v>
+        <v>160.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>56.17101727828425</v>
+        <v>32.91947951989722</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>14.8089814668023</v>
+        <v>21.53791141289782</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.9657392346545672</v>
+        <v>3.963199006012581</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0483272839293215</v>
+        <v>-0.218587768055575</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>7839</v>
+        <v>7769</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>414.7679540778267</v>
+        <v>538.9763644016301</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>43.75</v>
+        <v>5400</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,49 +2513,49 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>48.25996928901515</v>
+        <v>41.31489806218154</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>21.26417196180669</v>
+        <v>14.026011021877</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.005531904045683</v>
+        <v>0.6389495184223923</v>
       </c>
       <c r="K39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0973356774197344</v>
+        <v>-44.52705703315297</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7744</v>
+        <v>6863</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>410.3687805816338</v>
+        <v>508.4041155309562</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>480.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>40.82863248514141</v>
+        <v>48.50267088353775</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>25.01683191413792</v>
+        <v>20.82679699880605</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.4144703752137612</v>
+        <v>0.7543941387525872</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-6.367602580950915</v>
+        <v>0.9529822464291756</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6909</v>
+        <v>8011</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>409.1424592687371</v>
+        <v>507.7607920451196</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>47.4</v>
+        <v>16.45</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>60.90540333634534</v>
+        <v>54.38734344389023</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>36.10643528216789</v>
+        <v>28.57104183285978</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.27718768239296</v>
+        <v>0.3737074662559893</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.444876824824822</v>
+        <v>0.0134031146474185</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6840</v>
+        <v>6902</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>406.1294600679039</v>
+        <v>497.4276469321295</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>82.7</v>
+        <v>139</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,49 +2672,49 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>32.53489622950963</v>
+        <v>48.93191594884416</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>27.57427231882348</v>
+        <v>18.76579768946972</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6996290486386773</v>
+        <v>0.4545176765736896</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-2.469510310384763</v>
+        <v>-2.220501828371906</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>7799</v>
+        <v>7610</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>403.4287283454855</v>
+        <v>490.2407625490746</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>436.5</v>
+        <v>1405</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>41.8771761544644</v>
+        <v>33.68776712860648</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>33.0446006056744</v>
+        <v>16.69144112341567</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.3376076259995115</v>
+        <v>0.6816943418723231</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-14.5431125738674</v>
+        <v>-42.79692334354941</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6983</v>
+        <v>7721</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>394.221194921336</v>
+        <v>486.5954253655702</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>340</v>
+        <v>60.1</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>42.61965688460886</v>
+        <v>43.03826328608943</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>26.06729110382064</v>
+        <v>22.24696877481641</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.2817445423837512</v>
+        <v>0.3412712497515969</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-3.514501156467674</v>
+        <v>-0.1351738961259272</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6863</v>
+        <v>7747</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>393.4041155309562</v>
+        <v>486.4781762542236</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>110</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>48.50267058471597</v>
+        <v>51.5173027922524</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>20.82679699880605</v>
+        <v>6.093086191155119</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.7543941387525872</v>
+        <v>0.2541464522940806</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.9529822464291756</v>
+        <v>1.373476468618126</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6971</v>
+        <v>6859</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>384.9297131650718</v>
+        <v>484.3358036064449</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>24.7</v>
+        <v>113</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>53.17782047410243</v>
+        <v>40.36188210534527</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>20.69518740605048</v>
+        <v>27.2815877744456</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.8566659194435436</v>
+        <v>0.1335762794338545</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.189334119393461</v>
+        <v>-1.237798239071784</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6953</v>
+        <v>7765</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>377.9747050885037</v>
+        <v>481.9642799332588</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>233</v>
+        <v>232.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>42.26184525252159</v>
+        <v>49.48066024471284</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>19.05077658484898</v>
+        <v>27.84341671216186</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.3551230753349252</v>
+        <v>0.8668820354454581</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-2.45264067222252</v>
+        <v>-0.7542499845245103</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6937</v>
+        <v>7792</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>373.5986919836211</v>
+        <v>478.2518655261243</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>275.5</v>
+        <v>349.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>40.79611867512801</v>
+        <v>43.29934579619665</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>22.82630090769124</v>
+        <v>40.87552967960993</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6686005558268107</v>
+        <v>0.3716043502150292</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-3.786617266870642</v>
+        <v>-11.76257687671708</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>7610</v>
+        <v>7750</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>370.2407625490749</v>
+        <v>476.7282999264439</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>1405</v>
+        <v>1820</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>33.68776715858196</v>
+        <v>39.55472477534989</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>16.69144109993895</v>
+        <v>17.40444077966312</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6816943418723231</v>
+        <v>0.8169872968008624</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-42.7969233485966</v>
+        <v>-3.604861513540641</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>7734</v>
+        <v>6901</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>362.4223825827471</v>
+        <v>474.1926493072437</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2440</v>
+        <v>17.25</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>39.17323753736307</v>
+        <v>54.7375201643092</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14.6642944552655</v>
+        <v>30.84742216404097</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6936951239727788</v>
+        <v>0.7144457739141276</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-23.75503318045793</v>
+        <v>0.0427524653837453</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7750</v>
+        <v>6873</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>361.7282999264439</v>
+        <v>469.9377032028</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>1820</v>
+        <v>65.8</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>39.55472468351408</v>
+        <v>41.67649239868449</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>17.40444077840981</v>
+        <v>12.59556574654385</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.8169872968008624</v>
+        <v>0.8345773607699273</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-3.604861512098452</v>
+        <v>0.0808945137765972</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6901</v>
+        <v>7717</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>359.1926493072437</v>
+        <v>469.4005400020205</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>17.25</v>
+        <v>467</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>54.73752003337388</v>
+        <v>39.5999425895422</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>30.84742213851396</v>
+        <v>17.27250480982931</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7144457739141276</v>
+        <v>0.219660321070874</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0427524654318129</v>
+        <v>-17.9594855312418</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6994</v>
+        <v>6918</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>358.6983573067166</v>
+        <v>466.9341246948326</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>24.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>29.82909142311213</v>
+        <v>48.99579849745469</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>28.635950234626</v>
+        <v>29.79362502567208</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.409380642696588</v>
+        <v>0.2088811153711018</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.1089535321232579</v>
+        <v>0.0546391889552206</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>7828</v>
+        <v>7795</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>358.2851315719342</v>
+        <v>464.3212730868725</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>1505</v>
+        <v>444.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>30.61585644661364</v>
+        <v>35.53902466910101</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>18.81560408309556</v>
+        <v>20.17749128679742</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7285131571934247</v>
+        <v>0.9706434388802212</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>1</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-45.94985907730255</v>
+        <v>-8.746039579875855</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7703</v>
+        <v>6855</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>354.9206968149317</v>
+        <v>463.5375430553353</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>180</v>
+        <v>110.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>32.13524280953156</v>
+        <v>52.19549712435036</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>28.40058325534641</v>
+        <v>7.049562071100559</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4630823621595287</v>
+        <v>0.5241832404519658</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-3.180949356762111</v>
+        <v>2.761770349132869</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>7788</v>
+        <v>7855</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>347.2111835251408</v>
+        <v>459.8900115162654</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>280.5</v>
+        <v>41.4</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>44.58793325707848</v>
+        <v>27.57018469883698</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>18.45543524962371</v>
+        <v>52.82169084496779</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5852049606380428</v>
+        <v>0.6565856780707501</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-5.168744118684518</v>
+        <v>0.632510203745746</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>7747</v>
+        <v>6947</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>346.4781762542235</v>
+        <v>457.587660080416</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>110</v>
+        <v>66.8</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>51.51730278712344</v>
+        <v>37.80906331139215</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>6.093086191155119</v>
+        <v>13.20473695610323</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.2541464522940806</v>
+        <v>0.8958563622204405</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>1.373476468858476</v>
+        <v>0.0400678470621285</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6859</v>
+        <v>7812</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>稜研科技*-創</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>344.3358036064449</v>
+        <v>451.2405393398215</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>113</v>
+        <v>62.7</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>40.36188196809071</v>
+        <v>29.1798897587712</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>27.28158775006272</v>
+        <v>26.20018841638814</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.1335762794338545</v>
+        <v>0.6765130658826072</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-1.237798238711284</v>
+        <v>-0.2347956844070422</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>7765</v>
+        <v>6965</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>341.9642799332588</v>
+        <v>450.0738617410877</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>232.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>49.48066012233851</v>
+        <v>46.61014497085032</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>27.84341670076501</v>
+        <v>37.71441349651685</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.8668820354454581</v>
+        <v>0.3347771059966671</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.7542499846446908</v>
+        <v>0.6714286554662201</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7736</v>
+        <v>6913</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>339.6942432341141</v>
+        <v>444.2712200497297</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>68.3</v>
+        <v>132.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>43.37990944433815</v>
+        <v>47.67538842478525</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>25.94258612928862</v>
+        <v>19.36901206525929</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.1522843709810039</v>
+        <v>0.6588502806153753</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.1491805289245347</v>
+        <v>0.7826850912871122</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6949</v>
+        <v>6890</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>327.7556247478105</v>
+        <v>444.2529650876372</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>35.9</v>
+        <v>148</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>25.20255335846872</v>
+        <v>42.21529361631642</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>46.26143310369773</v>
+        <v>11.51953305282537</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.119455463943268</v>
+        <v>1.267904061030125</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>31.42793724393114</v>
+        <v>0.953011416649418</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6902</v>
+        <v>6962</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>327.4276469321295</v>
+        <v>437.0765247666964</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>139</v>
+        <v>31.1</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>48.93191593265379</v>
+        <v>42.77812659522586</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>18.7657977300304</v>
+        <v>13.18744944062119</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.4545176765736896</v>
+        <v>1.103855958830584</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-2.220501828804518</v>
+        <v>-0.1310806743230717</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6918</v>
+        <v>7791</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>326.9341246948327</v>
+        <v>436.9762081255942</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>48.9957985273228</v>
+        <v>25.00147691275839</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>29.79362502567208</v>
+        <v>39.16732768847643</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.2088811153711018</v>
+        <v>0.630583968631827</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.054639188931193</v>
+        <v>-0.3569587445966338</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>7728</v>
+        <v>6865</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>324.7669589752766</v>
+        <v>428.435092936604</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>544</v>
+        <v>28</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>31.2900057638351</v>
+        <v>52.89234744283804</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>22.10416625655124</v>
+        <v>14.08564172165894</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.00608970772557</v>
+        <v>1.40538262829086</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-7.421161980803478</v>
+        <v>-0.0125570288803001</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8011</v>
+        <v>7547</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>317.7607920451195</v>
+        <v>422.6027302131234</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>16.45</v>
+        <v>57.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>54.38734348748049</v>
+        <v>50.05293636816889</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>28.57104183285977</v>
+        <v>20.74398776439837</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.3737074662559893</v>
+        <v>0.430131597882921</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0134031146113625</v>
+        <v>-0.5322211942040789</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6947</v>
+        <v>7722</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>317.587660080416</v>
+        <v>422.5706869341356</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>66.8</v>
+        <v>253.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>37.80906332847048</v>
+        <v>35.59511388864728</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>13.20473698033222</v>
+        <v>12.44008447776265</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.8958563622204405</v>
+        <v>1.652521338269802</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0400678471342232</v>
+        <v>0.0468548050342194</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>7722</v>
+        <v>6967</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>307.5706869341362</v>
+        <v>419.7439758546421</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>253.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>35.59511363272827</v>
+        <v>47.06504666926688</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>12.4400845895796</v>
+        <v>17.34903659239215</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.652521338269802</v>
+        <v>0.4237345316653846</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0468548093604197</v>
+        <v>0.0062424216837455</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6890</v>
+        <v>8033</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>304.2529650876378</v>
+        <v>416.0552219526679</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>42.21529364193505</v>
+        <v>39.21563928978015</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>11.51953304412452</v>
+        <v>12.06730448975974</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.267904061030125</v>
+        <v>0.9702125923397884</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.9530114165292264</v>
+        <v>-0.7566541949313654</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8033</v>
+        <v>6919</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>301.0552219526679</v>
+        <v>415.6501985523553</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>161</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>39.21563925707731</v>
+        <v>35.68290382858963</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>12.06730467648976</v>
+        <v>32.64597786034507</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.9702125923397884</v>
+        <v>0.6414112112982376</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,11 +4121,11 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.7566541984163848</v>
+        <v>0.4197793187326017</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>299.9635282683184</v>
+        <v>414.9635282683184</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>110.5</v>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>46.68344625875548</v>
+        <v>46.68344636508867</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>20.0992460297607</v>
+        <v>20.09924603477925</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>1.144575313019181</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.9926056906460036</v>
+        <v>0.9926056893240968</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6862</v>
+        <v>7744</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>296.0689173903014</v>
+        <v>410.3687805816337</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>138.5</v>
+        <v>480.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>46.71225222686958</v>
+        <v>40.82863249193455</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>19.58416531992018</v>
+        <v>25.0168318980012</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.7142829105539473</v>
+        <v>0.4144703752137612</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.0331138417197505</v>
+        <v>-6.367602582753461</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6855</v>
+        <v>6840</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>293.5375430553353</v>
+        <v>406.1294600679039</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>110.5</v>
+        <v>82.7</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>52.19549711632595</v>
+        <v>32.53489629404581</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>7.049562055441458</v>
+        <v>27.57427233477704</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5241832404519658</v>
+        <v>0.6996290486386773</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>2.761770349613564</v>
+        <v>-2.469510309952151</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>7855</v>
+        <v>6887</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>289.8900115162653</v>
+        <v>403.5197027701514</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>41.4</v>
+        <v>35.9</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>27.57018469883698</v>
+        <v>44.09765907297963</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>52.82169084496779</v>
+        <v>25.51609822839613</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6565856780707501</v>
+        <v>0.6782041781097274</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.632510203745746</v>
+        <v>-0.2889524580415308</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6962</v>
+        <v>7799</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>287.0765247666964</v>
+        <v>403.4287283454855</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>31.1</v>
+        <v>436.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>42.77812661205805</v>
+        <v>41.87717614149223</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>13.1874494291543</v>
+        <v>33.04460066765011</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.103855958830584</v>
+        <v>0.3376076259995115</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.1310806742750064</v>
+        <v>-14.54311257506917</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6907</v>
+        <v>7760</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>284.1790589685822</v>
+        <v>402.9284555854834</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>171.5</v>
+        <v>32.2</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>41.34848120082877</v>
+        <v>41.39995132233852</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.56972160718723</v>
+        <v>33.25118313604685</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.3763762440701584</v>
+        <v>1.190065476346998</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-2.047609801396109</v>
+        <v>-0.0349646909400636</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>7547</v>
+        <v>6921</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>282.6027302131208</v>
+        <v>402.1888279818563</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>57.5</v>
+        <v>65.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>50.05293655039527</v>
+        <v>51.82011561253456</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>20.74398777183473</v>
+        <v>13.44560813351832</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.430131597882921</v>
+        <v>0.5170446799503476</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>1</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.5322211943242561</v>
+        <v>0.885731099120183</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>7805</v>
+        <v>6983</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>282.0604141501413</v>
+        <v>394.2211949213354</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>456.5</v>
+        <v>340</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>31.37239814599224</v>
+        <v>42.61965688835082</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>26.03314418709663</v>
+        <v>26.06729108576324</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.022176707826821</v>
+        <v>0.2817445423837512</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0304667453731752</v>
+        <v>-3.514501156587849</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6965</v>
+        <v>7856</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>漢測</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>280.0738617410878</v>
+        <v>389.056823419449</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>66.59999999999999</v>
+        <v>3470</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,49 +4580,49 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>46.61014484776288</v>
+        <v>33.85812790459512</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>37.71441349651686</v>
+        <v>17.27922466813992</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.3347771059966671</v>
+        <v>0.7645762096286033</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M78" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.6714286555863822</v>
+        <v>-107.3523722178471</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6967</v>
+        <v>7715</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>279.7439758546421</v>
+        <v>387.3082893008539</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>68.90000000000001</v>
+        <v>26.05</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>47.06504668941822</v>
+        <v>31.38844004180688</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>17.34903659714135</v>
+        <v>22.15154129071683</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.4237345316653846</v>
+        <v>0.9904839258629248</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0062424217077967</v>
+        <v>-0.0148331940528072</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6928</v>
+        <v>7704</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>277.8192056059987</v>
+        <v>382.1191992905974</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>45.2</v>
+        <v>59.9</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>45.33988127468886</v>
+        <v>42.79965725104962</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>14.16178163246019</v>
+        <v>17.04379764320185</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.7277594894593087</v>
+        <v>1.062671439290503</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.1195796331016381</v>
+        <v>-0.1241492456799821</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6919</v>
+        <v>6953</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>275.6501985523553</v>
+        <v>377.9747050885037</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>233</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>35.68290407163636</v>
+        <v>42.26184510629089</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>32.64597779142727</v>
+        <v>19.05077653469517</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6414112112982376</v>
+        <v>0.3551230753349252</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.4197793178914013</v>
+        <v>-2.452640670780465</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7856</v>
+        <v>7770</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>漢測</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>274.056823419449</v>
+        <v>374.2469387980522</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>3470</v>
+        <v>39.6</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>33.85812790459512</v>
+        <v>50.93513631756315</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>17.27922466813992</v>
+        <v>14.32328624018137</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.7645762096286033</v>
+        <v>0.5250353318360377</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-107.3523722178471</v>
+        <v>-0.3293218176641332</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>7689</v>
+        <v>6937</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>264.9062668801846</v>
+        <v>373.5986919836211</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>136.5</v>
+        <v>275.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>21.02438409622088</v>
+        <v>40.7961186681807</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>27.23911213706229</v>
+        <v>22.82630087293828</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3778405906129986</v>
+        <v>0.6686005558268107</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-1.656469276888302</v>
+        <v>-3.786617266029483</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>7827</v>
+        <v>6906</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>264.7105615066009</v>
+        <v>365.8759476867961</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>156.5</v>
+        <v>79</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>41.75622889706035</v>
+        <v>45.95075785517753</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>16.99773162014538</v>
+        <v>25.58946007501725</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6650052305848373</v>
+        <v>0.7281827722612416</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.8299810189159667</v>
+        <v>-0.5349626046970908</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7760</v>
+        <v>6910</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>262.928455585484</v>
+        <v>362.6118491401416</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>32.2</v>
+        <v>25.15</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>41.39995172163781</v>
+        <v>45.80299196370185</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>33.25118321442859</v>
+        <v>24.6973991332048</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.190065476346998</v>
+        <v>0.2858521735902291</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0349646912645305</v>
+        <v>-0.118758378445517</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>7842</v>
+        <v>7734</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>251.6966622814806</v>
+        <v>362.4223825827473</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>0</v>
+        <v>2440</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>29.79677016090002</v>
+        <v>39.17323750051565</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>14.73013441045355</v>
+        <v>14.66429438464531</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.09250388992281169</v>
+        <v>0.6936951239727788</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-4.82017221240967</v>
+        <v>-23.75503316964248</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>7715</v>
+        <v>6914</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>247.3082893008544</v>
+        <v>359.8686289112865</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>26.05</v>
+        <v>114.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>31.38843982697012</v>
+        <v>21.10455197461744</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>22.15154112336117</v>
+        <v>36.02126973674876</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.9904839258629248</v>
+        <v>1.499160914354524</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0148331934519402</v>
+        <v>0.2186147772173461</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6914</v>
+        <v>6994</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>244.8686289112864</v>
+        <v>358.6983573067166</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>114.5</v>
+        <v>24.6</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>21.10455263221004</v>
+        <v>29.82909136881036</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>36.02126955197815</v>
+        <v>28.63595018845679</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.499160914354524</v>
+        <v>1.409380642696588</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.2186147758954391</v>
+        <v>-0.1089535318108054</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7749</v>
+        <v>7828</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>242.3136220327533</v>
+        <v>358.2851315719342</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>330</v>
+        <v>1505</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,49 +5163,49 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>32.82219701897441</v>
+        <v>30.61585639594012</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>22.74471489779302</v>
+        <v>18.81560419886102</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.7199014376512305</v>
+        <v>0.7285131571934247</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-6.882433195444224</v>
+        <v>-45.94985906828947</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>7704</v>
+        <v>6949</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>242.1191992905974</v>
+        <v>357.7556247478105</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>59.9</v>
+        <v>35.9</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>42.79965725624128</v>
+        <v>25.20255357251538</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>17.04379764320186</v>
+        <v>46.26143325109632</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.062671439290503</v>
+        <v>1.119455463943268</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,11 +5234,11 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.1241492457520915</v>
+        <v>31.42793724557877</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>241.0598039865016</v>
+        <v>356.0598039865019</v>
       </c>
       <c r="E91" s="2" t="n">
         <v>34.15</v>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>37.00620066057708</v>
+        <v>37.00620064425139</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>17.54576888365285</v>
+        <v>17.54576889666607</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>1.543044635221404</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.1497689378955404</v>
+        <v>-0.1497689379556288</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>7821</v>
+        <v>7703</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>239.1747469457307</v>
+        <v>354.9206968149316</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>34.8</v>
+        <v>180</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>31.62844807865341</v>
+        <v>32.13524290244243</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>30.39455107751596</v>
+        <v>28.40058324024013</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.6735380655878551</v>
+        <v>0.4630823621595287</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0257175260143901</v>
+        <v>-3.180949355560376</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>7631</v>
+        <v>6955</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>236.6637630045845</v>
+        <v>353.024989896923</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>132</v>
+        <v>92.2</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>36.19072278521044</v>
+        <v>48.05912148967239</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>19.60422523839625</v>
+        <v>5.886072939808264</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.7563544615533195</v>
+        <v>1.330413391027636</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.7542636127304764</v>
+        <v>0.3861460569885566</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>7721</v>
+        <v>7788</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>236.5954253655724</v>
+        <v>347.2111835251408</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>60.1</v>
+        <v>280.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>43.03826311815038</v>
+        <v>44.58793325931139</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>22.24696868074389</v>
+        <v>18.45543527026573</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.3412712497515969</v>
+        <v>0.5852049606380428</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.1351738959096141</v>
+        <v>-5.16874411880469</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6921</v>
+        <v>7753</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>232.1888279818563</v>
+        <v>341.3760309174745</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>65.5</v>
+        <v>35.8</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>51.82011561253456</v>
+        <v>46.87390634553589</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>13.44560813351832</v>
+        <v>11.26270628130353</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5170446799503476</v>
+        <v>0.200438178748082</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.885731099120183</v>
+        <v>0.1105620655126886</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>7822</v>
+        <v>7705</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>228.7689205204762</v>
+        <v>334.3006191097743</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>797</v>
+        <v>29.45</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>32.00244438282424</v>
+        <v>37.92097126144625</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>19.25948755741602</v>
+        <v>11.75113032901653</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.702872682898685</v>
+        <v>1.595525441258109</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-17.86212553946775</v>
+        <v>-0.008976075851032101</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6865</v>
+        <v>6958</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>228.435092936604</v>
+        <v>333.0713740768032</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>28</v>
+        <v>16.95</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>52.89234745684931</v>
+        <v>45.76094383927838</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>14.08564171930181</v>
+        <v>16.56023754103104</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.40538262829086</v>
+        <v>0.9008546588732256</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0125570288803001</v>
+        <v>0.006335477625165</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6922</v>
+        <v>7820</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>225.3071020174571</v>
+        <v>330.1437698267983</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>192.5</v>
+        <v>100</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>41.08287796788005</v>
+        <v>50.99105338732877</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>16.93801859675543</v>
+        <v>11.5983644041793</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.7307077012688582</v>
+        <v>0.2592346335697399</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-2.352692515751631</v>
+        <v>1.943665653288344</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6910</v>
+        <v>7728</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>222.6118491401405</v>
+        <v>324.7669589752768</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>25.15</v>
+        <v>544</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>45.80299244184224</v>
+        <v>31.2900057697525</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>24.6973991332048</v>
+        <v>22.10416624532103</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.2858521735902291</v>
+        <v>1.00608970772557</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1187583783734155</v>
+        <v>-7.421161980322761</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>7812</v>
+        <v>7803</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>稜研科技*-創</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>216.2405393398216</v>
+        <v>318.6360313515769</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>62.7</v>
+        <v>17.25</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>29.17988954758755</v>
+        <v>40.94027920357652</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>26.20018838037585</v>
+        <v>17.99143397085533</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6765130658826072</v>
+        <v>0.3234957453752536</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.2347956841666971</v>
+        <v>0.0395050636844821</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6955</v>
+        <v>6931</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>213.0249898969245</v>
+        <v>313.1125685469111</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>92.2</v>
+        <v>38.05</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>48.05912145779619</v>
+        <v>35.94853523197</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>5.886072939808261</v>
+        <v>16.0741483662233</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.330413391027636</v>
+        <v>0.8414157787048602</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.3861460574692716</v>
+        <v>0.0306768383237172</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>7791</v>
+        <v>7818</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>211.9762081255945</v>
+        <v>313.0479827972452</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>50.6</v>
+        <v>59.2</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>25.00147718474393</v>
+        <v>34.09924289025214</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>39.16732772170074</v>
+        <v>16.67384582710971</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.630583968631827</v>
+        <v>1.237273957977922</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.3569587448369826</v>
+        <v>-0.0138852129518333</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7770</v>
+        <v>6951</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>204.2469387980561</v>
+        <v>312.0321745504469</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>39.6</v>
+        <v>68</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>50.93513623930242</v>
+        <v>32.51709021086891</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>14.32328629194084</v>
+        <v>36.67097088884139</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5250353318360377</v>
+        <v>0.7990980564313366</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.3293218171113388</v>
+        <v>-0.0245719878433468</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>7753</v>
+        <v>7823</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>201.3760309174744</v>
+        <v>304.9814706289757</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>35.8</v>
+        <v>75.7</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>46.87390670266685</v>
+        <v>35.30485926787375</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>11.26270622325753</v>
+        <v>20.69984214467488</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.200438178748082</v>
+        <v>1.398147062897572</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.1105620654646168</v>
+        <v>-0.3569874199686442</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>7825</v>
+        <v>6899</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>和亞智慧</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>199.1141721640624</v>
+        <v>296.0781308731458</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>68.5</v>
+        <v>49.05</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>37.72887213959283</v>
+        <v>43.53571231483721</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>17.17731532916835</v>
+        <v>23.51279201428196</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4156886981472209</v>
+        <v>1.326147578122985</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-1.305557301773376</v>
+        <v>-0.0286414627900757</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6906</v>
+        <v>6862</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>195.875947686796</v>
+        <v>296.0689173903014</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>79</v>
+        <v>138.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>45.95075737993496</v>
+        <v>46.71225230609953</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>25.58946008807905</v>
+        <v>19.58416539117608</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.7281827722612416</v>
+        <v>0.7142829105539473</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.5349626044567526</v>
+        <v>-0.0331138423205948</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>7705</v>
+        <v>6854</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>194.3006191097751</v>
+        <v>295.3456061077069</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>29.45</v>
+        <v>90.3</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>37.92097135251654</v>
+        <v>43.92838794372479</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>11.75113038631652</v>
+        <v>12.9134848383941</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.595525441258109</v>
+        <v>0.4834790989365228</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0089760758630506</v>
+        <v>-0.1600559965878075</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6958</v>
+        <v>8034</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>193.0713740768034</v>
+        <v>294.4269399407568</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>16.95</v>
+        <v>19.15</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>45.76094388105785</v>
+        <v>40.55633538081413</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>16.56023754103104</v>
+        <v>15.33454964237602</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.9008546588732256</v>
+        <v>0.3397115064718624</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0063354776131486</v>
+        <v>-0.09296872100903079</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>7823</v>
+        <v>7780</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>189.9814706289757</v>
+        <v>291.8446907004526</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>75.7</v>
+        <v>15.9</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>35.30485926787375</v>
+        <v>41.38329729952854</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>20.69984214467488</v>
+        <v>15.52802684784326</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.398147062897572</v>
+        <v>1.127373979340273</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.3569874199686442</v>
+        <v>0.0120699093930326</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6873</v>
+        <v>6969</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>189.9377032028</v>
+        <v>285.7395300425751</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>65.8</v>
+        <v>28.6</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>41.67649142769587</v>
+        <v>35.42386820435318</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>12.59556604174129</v>
+        <v>12.06479378573508</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.8345773607699273</v>
+        <v>0.1589818762115166</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0808945169010872</v>
+        <v>-0.1948585151305297</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8024</v>
+        <v>6907</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>179.4611452546743</v>
+        <v>284.1790589685822</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>11.95</v>
+        <v>171.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>34.47408709064854</v>
+        <v>41.34848120082877</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>19.7097992725815</v>
+        <v>13.56972160718723</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5336167944208839</v>
+        <v>0.3763762440701584</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0068829161703944</v>
+        <v>-2.047609801396109</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6931</v>
+        <v>7805</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>173.1125685469118</v>
+        <v>282.0604141501413</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>38.05</v>
+        <v>456.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>35.94853530807001</v>
+        <v>31.37239827726428</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>16.07414837767192</v>
+        <v>26.03314411741996</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.8414157787048602</v>
+        <v>1.022176707826821</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0306768382756505</v>
+        <v>-0.0304667453731752</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>7818</v>
+        <v>6923</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>173.0479827972453</v>
+        <v>275.7898977533308</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>59.2</v>
+        <v>72.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>34.09924201154645</v>
+        <v>32.58684638992757</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.67384587745565</v>
+        <v>11.74454125498137</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.237273957977922</v>
+        <v>0.7789897753330763</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0138852117501029</v>
+        <v>-0.1563354997772587</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6951</v>
+        <v>6908</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>172.0321745504469</v>
+        <v>268.0746438486202</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>68</v>
+        <v>25.05</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>32.51709013533166</v>
+        <v>22.75176200047441</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>36.6709709223761</v>
+        <v>15.8929164531567</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.7990980564313366</v>
+        <v>0.3265486658176299</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0245719877231738</v>
+        <v>-0.0761509266042157</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6969</v>
+        <v>7689</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>170.7395300425751</v>
+        <v>264.9062668801846</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>28.6</v>
+        <v>136.5</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>35.42386812818344</v>
+        <v>21.02438409622088</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>12.06479377969144</v>
+        <v>27.23911213706229</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.1589818762115166</v>
+        <v>0.3778405906129986</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.1948585150464102</v>
+        <v>-1.656469276888302</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>7768</v>
+        <v>7827</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>170.0182315513023</v>
+        <v>264.7105615066012</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>269.5</v>
+        <v>156.5</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>38.26453406391065</v>
+        <v>41.75622890540421</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>19.92785722866304</v>
+        <v>16.9977316600184</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.715002905025412</v>
+        <v>0.6650052305848373</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-3.312074466696708</v>
+        <v>-0.829981018771786</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>7402</v>
+        <v>7842</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>160.8626624095594</v>
+        <v>251.6966622814806</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>92.3</v>
+        <v>0</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>31.39065005821747</v>
+        <v>29.79677015980528</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>16.60494958134369</v>
+        <v>14.73013442825086</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.8312621671598301</v>
+        <v>0.09250388992281169</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.4525931043211375</v>
+        <v>-4.820172212650012</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6899</v>
+        <v>7732</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>156.0781308731458</v>
+        <v>249.5756740252476</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>49.05</v>
+        <v>33.1</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>43.53571218494147</v>
+        <v>50.83678398947242</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>23.51279203591104</v>
+        <v>5.291853592397198</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.326147578122985</v>
+        <v>0.6418341768716171</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.028641462766037</v>
+        <v>0.3389087607722496</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6854</v>
+        <v>7749</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>155.3456061077073</v>
+        <v>242.3136220327533</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>90.3</v>
+        <v>330</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>43.92838806717737</v>
+        <v>32.82219696093709</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>12.91348485242387</v>
+        <v>22.74471489779302</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.4834790989365228</v>
+        <v>0.7199014376512305</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.1600559973088458</v>
+        <v>-6.882433199289736</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>8034</v>
+        <v>7821</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>154.4269399407604</v>
+        <v>239.1747469457308</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>19.15</v>
+        <v>34.8</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>40.55633626212938</v>
+        <v>31.6284485316256</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.33454952016925</v>
+        <v>30.39455135341452</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.3397115064718624</v>
+        <v>0.6735380655878551</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>1</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.09296872134551699</v>
+        <v>0.0257175263628879</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6895</v>
+        <v>7631</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>154.2544714243012</v>
+        <v>236.6637630045845</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>45.29852918333143</v>
+        <v>36.19072278521044</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>16.35242486429531</v>
+        <v>19.60422529281434</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.4784843644138908</v>
+        <v>0.7563544615533195</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.992733700571975</v>
+        <v>-0.7542636133313247</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6887</v>
+        <v>7822</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>153.5197027701517</v>
+        <v>228.7689205204762</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>35.9</v>
+        <v>797</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>44.09765905647114</v>
+        <v>32.00244445181791</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>25.51609822839613</v>
+        <v>19.25948758860384</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.6782041781097274</v>
+        <v>0.702872682898685</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.288952457993461</v>
+        <v>-17.86212553946775</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6908</v>
+        <v>6922</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>153.0746438486202</v>
+        <v>225.307102017457</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>25.05</v>
+        <v>192.5</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>22.75176213671565</v>
+        <v>41.08287804048542</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>15.8929164531567</v>
+        <v>16.93801858718306</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.3265486658176299</v>
+        <v>0.7307077012688582</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0761509265321114</v>
+        <v>-2.352692514189385</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>7780</v>
+        <v>7825</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>和亞智慧</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>151.8446907004526</v>
+        <v>199.1141721640624</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>15.9</v>
+        <v>68.5</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>41.3833034214878</v>
+        <v>37.72887211307818</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>15.52801824363553</v>
+        <v>17.17731535288038</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.127373979340273</v>
+        <v>0.4156886981472209</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0120699063418399</v>
+        <v>-1.30555730143592</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6923</v>
+        <v>8024</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>135.7898977533308</v>
+        <v>179.4611452546743</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>72.5</v>
+        <v>11.95</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>32.58684664152992</v>
+        <v>34.47408709064854</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>11.74454124479512</v>
+        <v>19.70979923646518</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.7789897753330763</v>
+        <v>0.5336167944208839</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.1563354996570891</v>
+        <v>-0.0068829161944282</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>7820</v>
+        <v>7768</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>130.1437698267985</v>
+        <v>170.0182315513023</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>100</v>
+        <v>269.5</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>50.99105336288381</v>
+        <v>38.26453425351328</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>11.59836435695464</v>
+        <v>19.92785721802236</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.2592346335697399</v>
+        <v>0.715002905025412</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>1.943665654490075</v>
+        <v>-3.312074465975732</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>7732</v>
+        <v>7402</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>109.5756740252476</v>
+        <v>160.8626624095594</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>33.1</v>
+        <v>92.3</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>50.83678398361938</v>
+        <v>31.39064980882399</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>5.291853571540626</v>
+        <v>16.6049494194112</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.6418341768716171</v>
+        <v>0.8312621671598301</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.3389087608323345</v>
+        <v>-0.4525931019176699</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7205,21 +7205,21 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>7803</v>
+        <v>6895</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>38.6360313515769</v>
+        <v>154.2544714243012</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>17.25</v>
+        <v>145</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>40.94027911256831</v>
+        <v>45.29852895051504</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>17.99143394710669</v>
+        <v>16.35242489427674</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.3234957453752536</v>
+        <v>0.4784843644138908</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,11 +7248,11 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.039505063804655</v>
+        <v>-0.9927336998509272</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
